--- a/02_DIA_inicio_2026_analisis_assets/rbd_9730_colegio-antu_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9730_colegio-antu_nt1_rubricas.xlsx
@@ -1968,13 +1968,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59AE5F47-1FDF-4F2D-8466-165FBA7E8C3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5249F474-E8A7-4A04-AE82-ADE7512D68C7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB1B6FB4-B485-4B11-B820-D7169E9F59D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C83111A5-9514-49B7-B0F9-06F9E0749322}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC74E2B8-C069-429B-9F63-0044B07699CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DDC8CFC-576F-4175-9BBC-F23B604D7808}"/>
 </file>